--- a/utils/monday_sprint_sprint_2023-23.xlsx
+++ b/utils/monday_sprint_sprint_2023-23.xlsx
@@ -3787,7 +3787,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>111</v>

--- a/utils/monday_sprint_sprint_2023-23.xlsx
+++ b/utils/monday_sprint_sprint_2023-23.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="205">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>17485</t>
+    <t>4812025942</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>14/07/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>18/11/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>22015</t>
+    <t>5470713463</t>
   </si>
   <si>
     <t>Relatório PCP: “Saldo de Peças por Setor</t>
@@ -111,19 +111,19 @@
     <t>07/11/2023</t>
   </si>
   <si>
+    <t>16/11/2023</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Novembro</t>
   </si>
   <si>
-    <t>22801</t>
+    <t>5365901860</t>
   </si>
   <si>
     <t>Teste de quebra d´água</t>
@@ -132,16 +132,22 @@
     <t>20/10/2023</t>
   </si>
   <si>
+    <t>08/11/2023</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Outubro</t>
   </si>
   <si>
+    <t>5470722248</t>
+  </si>
+  <si>
     <t>Relatório Faturamento: “Relatórios &gt; Saldo do Estoque no Depósito Fabril por Modelo</t>
   </si>
   <si>
-    <t>22342</t>
+    <t>5209491089</t>
   </si>
   <si>
     <t>Espelho de Nota Fiscal</t>
@@ -150,6 +156,9 @@
     <t>22/09/2023</t>
   </si>
   <si>
+    <t>22/10/2023</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
@@ -159,13 +168,16 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>22660</t>
+    <t>5366153686</t>
   </si>
   <si>
     <t>Padronizar telas sistema de corridas</t>
   </si>
   <si>
-    <t>23088</t>
+    <t>14/11/2023</t>
+  </si>
+  <si>
+    <t>5443287561</t>
   </si>
   <si>
     <t>Fluxo ACVO Eletrônica</t>
@@ -174,112 +186,124 @@
     <t>02/11/2023</t>
   </si>
   <si>
-    <t>23084</t>
+    <t>5443309683</t>
   </si>
   <si>
     <t>Criar campo de pergunta para preenchimento sistemas de corridas</t>
   </si>
   <si>
-    <t>23043</t>
+    <t>06/11/2023</t>
+  </si>
+  <si>
+    <t>5443542002</t>
   </si>
   <si>
     <t>Inserir campo na impressão da OS</t>
   </si>
   <si>
-    <t>23041</t>
+    <t>5443566702</t>
   </si>
   <si>
     <t>Pre lista em dispositivo móvel</t>
   </si>
   <si>
-    <t>23037</t>
+    <t>5443612188</t>
   </si>
   <si>
     <t>Filtro de relatório</t>
   </si>
   <si>
-    <t>23029</t>
+    <t>5443620759</t>
   </si>
   <si>
     <t>Melhoria no Sistema Tratamento Térmico Controle de Processos</t>
   </si>
   <si>
-    <t>23012</t>
+    <t>5443654365</t>
   </si>
   <si>
     <t>WMS - Logística interna 1</t>
   </si>
   <si>
-    <t>23016</t>
+    <t>5443703406</t>
   </si>
   <si>
     <t>WMS - Logística interna 5</t>
   </si>
   <si>
-    <t>23015</t>
+    <t>13/11/2023</t>
+  </si>
+  <si>
+    <t>5443703422</t>
   </si>
   <si>
     <t>WMS - Logística interna 4</t>
   </si>
   <si>
-    <t>23013</t>
+    <t>5443738112</t>
   </si>
   <si>
     <t>WMS - Logística interna 2</t>
   </si>
   <si>
-    <t>23011</t>
+    <t>09/11/2023</t>
+  </si>
+  <si>
+    <t>5443751983</t>
   </si>
   <si>
     <t>Log de eventos</t>
   </si>
   <si>
-    <t>23010</t>
+    <t>5443767574</t>
   </si>
   <si>
     <t>Nova coluna Prévia MPS Dep</t>
   </si>
   <si>
-    <t>23006</t>
+    <t>5443783980</t>
   </si>
   <si>
     <t>Peso peças Estornadas no Dep (Arq. MPS)</t>
   </si>
   <si>
-    <t>22952</t>
+    <t>5443869199</t>
   </si>
   <si>
     <t>Consulta OTF de Conjunto/Item Comercial</t>
   </si>
   <si>
-    <t>22900</t>
+    <t>5443882442</t>
   </si>
   <si>
     <t>Nova aba sistema de modelos</t>
   </si>
   <si>
-    <t>22878</t>
+    <t>5443890361</t>
   </si>
   <si>
     <t>Atualização sistema de modelos</t>
   </si>
   <si>
-    <t>22733</t>
+    <t>5443900246</t>
   </si>
   <si>
     <t>Geração de Relatório data CPC / Pedido</t>
   </si>
   <si>
+    <t>5507454980</t>
+  </si>
+  <si>
     <t>Padronizar telas sistema de corridas - WorkPanels</t>
   </si>
   <si>
-    <t>14/11/2023</t>
+    <t>5507456876</t>
   </si>
   <si>
     <t>Padronizar telas sistema de corridas - Transações</t>
   </si>
   <si>
-    <t>22972</t>
+    <t>5443846516</t>
   </si>
   <si>
     <t>Integração das informações de proforma/invoices - Benner</t>
@@ -291,13 +315,13 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>22843</t>
+    <t>5470754164</t>
   </si>
   <si>
     <t>Alteração relatório de invoices</t>
   </si>
   <si>
-    <t>21214</t>
+    <t>5125537767</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -309,13 +333,16 @@
     <t>07/09/2023</t>
   </si>
   <si>
+    <t>24/10/2023</t>
+  </si>
+  <si>
     <t>5367244494</t>
   </si>
   <si>
     <t>Projeto Fatura  Homologação</t>
   </si>
   <si>
-    <t>18631</t>
+    <t>5391053238</t>
   </si>
   <si>
     <t>Novo relatório - Relatório de Custos por Nota Fiscal</t>
@@ -327,19 +354,16 @@
     <t>25/10/2023</t>
   </si>
   <si>
-    <t>23126</t>
+    <t>5474930895</t>
   </si>
   <si>
     <t>Senha Registro Moldagem</t>
   </si>
   <si>
-    <t>08/11/2023</t>
-  </si>
-  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>22466</t>
+    <t>5291082030</t>
   </si>
   <si>
     <t>Validação Ajustagem em tablets</t>
@@ -348,7 +372,7 @@
     <t>06/10/2023</t>
   </si>
   <si>
-    <t>22014</t>
+    <t>5305576534</t>
   </si>
   <si>
     <t>Integrar Compras SPOT com NIMBI</t>
@@ -357,58 +381,73 @@
     <t>10/10/2023</t>
   </si>
   <si>
+    <t>19/11/2023</t>
+  </si>
+  <si>
+    <t>5141379440</t>
+  </si>
+  <si>
     <t>Geração do relatório PDI - Versão do cliente</t>
   </si>
   <si>
     <t>11/09/2023</t>
   </si>
   <si>
+    <t>15/11/2023</t>
+  </si>
+  <si>
+    <t>5221048384</t>
+  </si>
+  <si>
     <t>Criar tela de aprovação no PDI e ENDs, conforme fluxo de aprovações</t>
   </si>
   <si>
     <t>25/09/2023</t>
   </si>
   <si>
+    <t>5221060050</t>
+  </si>
+  <si>
     <t>Fazer a movimentação no SPS ao finalizar a ajustagem.</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>5367185671</t>
   </si>
   <si>
     <t>Produtivo em horas - Homologação</t>
   </si>
   <si>
-    <t>21798</t>
+    <t>5138487918</t>
   </si>
   <si>
     <t>Criar tela para editar e aprovar o apontamento (Ajustagem)</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>5367461090</t>
   </si>
   <si>
     <t>Sistema Novo de Revisão de Documentos</t>
   </si>
   <si>
-    <t>22764</t>
+    <t>5365989018</t>
   </si>
   <si>
     <t>Impressora Zebra</t>
   </si>
   <si>
+    <t>5384631151</t>
+  </si>
+  <si>
     <t>Impressão de outras identificações da embalagens</t>
   </si>
   <si>
-    <t>24/10/2023</t>
-  </si>
-  <si>
-    <t>23064</t>
+    <t>5443507710</t>
   </si>
   <si>
     <t>Bloqueio de movimentação - END</t>
   </si>
   <si>
-    <t>23052</t>
+    <t>5443525362</t>
   </si>
   <si>
     <t>Encerramento automático de apontamento de Produção</t>
@@ -435,43 +474,58 @@
     <t>Sistemas</t>
   </si>
   <si>
-    <t>21967</t>
+    <t>5443947879</t>
   </si>
   <si>
     <t>Ajuste de Impressão de Etiqueta padrão Altona (Reincidente)</t>
   </si>
   <si>
+    <t>5458438641</t>
+  </si>
+  <si>
     <t>Enviar dados da nota fiscal*</t>
   </si>
   <si>
-    <t>06/11/2023</t>
+    <t>5458442421</t>
   </si>
   <si>
     <t>Testar compras SPOT</t>
   </si>
   <si>
-    <t>22382</t>
+    <t>05/11/2023</t>
+  </si>
+  <si>
+    <t>5458561470</t>
   </si>
   <si>
     <t>Grupos de perfil de usuário</t>
   </si>
   <si>
+    <t>5507437421</t>
+  </si>
+  <si>
     <t>Sistema Novo de Revisão de Documentos - Correções</t>
   </si>
   <si>
+    <t>5507440347</t>
+  </si>
+  <si>
     <t>Sistema Novo de Revisão de Documentos - Alteração no Checlist</t>
   </si>
   <si>
+    <t>5507443707</t>
+  </si>
+  <si>
     <t>Sistema Novo de Revisão de Documentos - E-mail</t>
   </si>
   <si>
-    <t>22949</t>
+    <t>5458600924</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Modelos Revenda -  TESTAR</t>
   </si>
   <si>
-    <t>22948</t>
+    <t>5458600998</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Itens Comerciais - TESTAR</t>
@@ -486,6 +540,9 @@
     <t>Atividades Diversas</t>
   </si>
   <si>
+    <t>20/11/2023</t>
+  </si>
+  <si>
     <t>5468619715</t>
   </si>
   <si>
@@ -498,7 +555,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-23</t>
+    <t>Jul/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -1131,13 +1188,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -1178,7 +1235,7 @@
         <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1187,15 +1244,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1207,10 +1264,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1225,13 +1282,13 @@
         <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>34</v>
@@ -1242,7 +1299,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1254,10 +1311,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1269,27 +1326,27 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1301,10 +1358,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1319,7 +1376,7 @@
         <v>38</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1328,15 +1385,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1348,10 +1405,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1363,7 +1420,7 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>24</v>
@@ -1383,7 +1440,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1395,10 +1452,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1410,10 +1467,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1430,7 +1487,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1442,25 +1499,25 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1477,7 +1534,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1489,10 +1546,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1504,10 +1561,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1524,7 +1581,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1536,10 +1593,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1551,10 +1608,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1571,7 +1628,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1583,10 +1640,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1598,10 +1655,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1618,7 +1675,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1630,10 +1687,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1645,10 +1702,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1665,7 +1722,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1677,10 +1734,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1692,10 +1749,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1712,7 +1769,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1724,10 +1781,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1739,10 +1796,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1759,7 +1816,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1771,10 +1828,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1786,10 +1843,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1806,7 +1863,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1818,10 +1875,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1833,10 +1890,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1853,7 +1910,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1865,10 +1922,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1880,10 +1937,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1900,7 +1957,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1912,10 +1969,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1927,10 +1984,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1947,7 +2004,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1959,10 +2016,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1974,10 +2031,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1994,7 +2051,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2006,10 +2063,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2021,10 +2078,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2041,7 +2098,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2053,10 +2110,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2068,10 +2125,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2088,7 +2145,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2100,10 +2157,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2115,10 +2172,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2135,7 +2192,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2147,10 +2204,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2162,10 +2219,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2182,7 +2239,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2194,10 +2251,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2209,10 +2266,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2229,7 +2286,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2241,13 +2298,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2256,16 +2313,16 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>34</v>
@@ -2276,7 +2333,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2288,10 +2345,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2306,13 +2363,13 @@
         <v>31</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>34</v>
@@ -2323,22 +2380,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2350,42 +2407,42 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>34</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2400,24 +2457,24 @@
         <v>38</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2429,13 +2486,13 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2444,27 +2501,27 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2476,10 +2533,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2491,13 +2548,13 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>26</v>
@@ -2511,7 +2568,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2523,10 +2580,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2538,10 +2595,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2553,30 +2610,30 @@
         <v>34</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2585,10 +2642,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2600,27 +2657,27 @@
         <v>27</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2632,10 +2689,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2647,12 +2704,12 @@
         <v>27</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2664,10 +2721,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2679,10 +2736,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2691,15 +2748,15 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2711,10 +2768,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2726,10 +2783,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2738,30 +2795,30 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2776,7 +2833,7 @@
         <v>38</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2785,30 +2842,30 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2820,10 +2877,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2835,27 +2892,27 @@
         <v>27</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2870,7 +2927,7 @@
         <v>38</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2879,15 +2936,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2899,10 +2956,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2917,7 +2974,7 @@
         <v>38</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2926,15 +2983,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2946,10 +3003,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2961,10 +3018,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2973,15 +3030,15 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2993,10 +3050,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3008,7 +3065,7 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
@@ -3028,7 +3085,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3040,10 +3097,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3055,10 +3112,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3075,37 +3132,37 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3122,7 +3179,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3134,10 +3191,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3149,10 +3206,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3169,25 +3226,25 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>21</v>
@@ -3196,10 +3253,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3216,25 +3273,25 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>21</v>
@@ -3243,10 +3300,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3263,25 +3320,25 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>21</v>
@@ -3290,10 +3347,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3310,22 +3367,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3337,10 +3394,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3357,22 +3414,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3384,10 +3441,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3404,22 +3461,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3431,7 +3488,7 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>24</v>
@@ -3451,7 +3508,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3463,10 +3520,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3478,10 +3535,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3498,7 +3555,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3510,10 +3567,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3525,10 +3582,10 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3545,25 +3602,25 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>21</v>
@@ -3575,7 +3632,7 @@
         <v>31</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3592,25 +3649,25 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>21</v>
@@ -3622,7 +3679,7 @@
         <v>31</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3639,25 +3696,25 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>21</v>
@@ -3669,7 +3726,7 @@
         <v>31</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3697,23 +3754,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3721,16 +3778,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3741,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>19.02</v>
       </c>
       <c r="J5" s="4">
         <v>2</v>
@@ -3749,7 +3806,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3762,7 +3819,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -3770,7 +3827,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3801,12 +3858,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B2">
         <v>56</v>
@@ -3820,7 +3877,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3830,25 +3887,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3865,13 +3922,13 @@
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3886,24 +3943,24 @@
         <v>34</v>
       </c>
       <c r="Q10">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E11">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -3912,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="K11">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
         <v>48</v>
-      </c>
-      <c r="M11" t="s">
-        <v>45</v>
       </c>
       <c r="N11">
         <v>4</v>
@@ -3924,12 +3981,12 @@
         <v>27</v>
       </c>
       <c r="Q11">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3941,53 +3998,47 @@
         <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N13">
         <v>2</v>
       </c>
-      <c r="P13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="M14" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -3995,7 +4046,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4003,7 +4054,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4011,7 +4062,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4019,10 +4070,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4030,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4038,142 +4089,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>64</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
